--- a/2026IAD214_Jennifer_Cabintoy_test_output.xlsx
+++ b/2026IAD214_Jennifer_Cabintoy_test_output.xlsx
@@ -124,7 +124,7 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Nonconformity With The Written Policies, Guidelines, Process And Procedures -4</t>
+    <t>Ignore or Disregard Office/Operation Best Practices -3</t>
   </si>
   <si>
     <t>INCOMPLETE DETAILS IN PCV - APPROVED BY</t>
@@ -660,13 +660,13 @@
         <v>43</v>
       </c>
       <c r="W2">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X2">
         <v>0</v>
       </c>
       <c r="Y2">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Z2" t="s">
         <v>44</v>
